--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-11-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.90</t>
+          <t>£9.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.90</t>
+          <t>£9.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.90</t>
+          <t>£9.83</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -780,17 +780,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.75</t>
+          <t>£18.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.75</t>
+          <t>£18.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.75</t>
+          <t>£18.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1990,17 +1990,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£39.45</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£39.45</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£39.45</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£37.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£37.72</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£37.72</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>£29.82</t>
+          <t>£27.44</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£36.74</t>
+          <t>£33.81</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£40.21</t>
+          <t>£36.68</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64499e8e5+80021]
-	GetHandleVerifier [0x0x7ff64499e940+80112]
-	(No symbol) [0x0x7ff64472060f]
-	(No symbol) [0x0x7ff644778854]
-	(No symbol) [0x0x7ff644778b1c]
-	(No symbol) [0x0x7ff6447cc927]
-	(No symbol) [0x0x7ff6447a126f]
-	(No symbol) [0x0x7ff6447c968a]
-	(No symbol) [0x0x7ff6447a1003]
-	(No symbol) [0x0x7ff6447695d1]
-	(No symbol) [0x0x7ff64476a3f3]
-	GetHandleVerifier [0x0x7ff644c5dc7d+2960429]
-	GetHandleVerifier [0x0x7ff644c57f3a+2936554]
-	GetHandleVerifier [0x0x7ff644c78977+3070247]
-	GetHandleVerifier [0x0x7ff6449b83ce+185214]
-	GetHandleVerifier [0x0x7ff6449bfe1f+216527]
-	GetHandleVerifier [0x0x7ff6449a7b24+117460]
-	GetHandleVerifier [0x0x7ff6449a7cdf+117903]
-	GetHandleVerifier [0x0x7ff64498dbb8+11112]
+	GetHandleVerifier [0x0x7ff6f64be8e5+80021]
+	GetHandleVerifier [0x0x7ff6f64be940+80112]
+	(No symbol) [0x0x7ff6f624060f]
+	(No symbol) [0x0x7ff6f6298854]
+	(No symbol) [0x0x7ff6f6298b1c]
+	(No symbol) [0x0x7ff6f62ec927]
+	(No symbol) [0x0x7ff6f62c126f]
+	(No symbol) [0x0x7ff6f62e968a]
+	(No symbol) [0x0x7ff6f62c1003]
+	(No symbol) [0x0x7ff6f62895d1]
+	(No symbol) [0x0x7ff6f628a3f3]
+	GetHandleVerifier [0x0x7ff6f677dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6f6777f3a+2936554]
+	GetHandleVerifier [0x0x7ff6f6798977+3070247]
+	GetHandleVerifier [0x0x7ff6f64d83ce+185214]
+	GetHandleVerifier [0x0x7ff6f64dfe1f+216527]
+	GetHandleVerifier [0x0x7ff6f64c7b24+117460]
+	GetHandleVerifier [0x0x7ff6f64c7cdf+117903]
+	GetHandleVerifier [0x0x7ff6f64adbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1229.44</t>
+          <t>£1259.52</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
